--- a/results/LCA/lci_comparison_ab/copper_LCIA-results.xlsx
+++ b/results/LCA/lci_comparison_ab/copper_LCIA-results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="54">
   <si>
     <t>index</t>
   </si>
@@ -43,46 +43,139 @@
     <t>IMPACT World+ Damage 2.1 for ecoinvent v3.10 | Human health | Total human health</t>
   </si>
   <si>
-    <t>copper, cathode | market for copper, cathode | World | kilogram | premise_generated_db_2025_L</t>
-  </si>
-  <si>
-    <t>copper concentrate, sulfide ore | copper mine operation and beneficiation, sulfide ore | CA | kilogram | premise_generated_db_2025_L</t>
-  </si>
-  <si>
-    <t>copper concentrate, sulfide ore | market for copper concentrate, sulfide ore | World | kilogram | premise_generated_db_2025_L</t>
-  </si>
-  <si>
-    <t>copper, cathode | copper production, cathode, solvent extraction and electrowinning process | CA | kilogram | premise_generated_db_2025_L</t>
+    <t>cu concentrate | open-pit mining and beneficiation at Highland Valley | CA-BC | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>copper, cathode | market for copper, cathode | World | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>cu concentrate | open-pit mining and beneficiation at Copper Mountain | CA-BC | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>cu concentrate | underground mining and beneficiation at LaRonde | CA-QC | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>cu concentrate | market for Cu concentrate | CA | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>cu concentrate | underground mining and beneficiation at New Afton | CA-BC | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>copper, cathode | copper production, cathode, solvent extraction and electrowinning process | CA | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>cu concentrate | underground mining and beneficiation at Goldex | CA-QC | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>cu concentrate | open-pit mining and beneficiation at Gibraltar | CA-BC | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>cu cathode | copper (Cu) global market | GLO | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>cu concentrate | underground mining and beneficiation at Snow Lake | CA-MB | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>copper concentrate, sulfide ore | market for copper concentrate, sulfide ore | World | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>cu concentrate | underground mining and beneficiation at Kidd Creek | CA-ON | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>cu concentrate | open-pit mining and beneficiation at Mount Milligan | CA-BC | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>copper concentrate, sulfide ore | copper mine operation and beneficiation, sulfide ore | CA | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>cu concentrate | open-pit mining and beneficiation at Mount Polley | CA-BC | kilogram | premise_db_2025_L</t>
   </si>
   <si>
     <t>kilogram</t>
   </si>
   <si>
+    <t>cu concentrate</t>
+  </si>
+  <si>
     <t>copper, cathode</t>
   </si>
   <si>
+    <t>cu cathode</t>
+  </si>
+  <si>
     <t>copper concentrate, sulfide ore</t>
   </si>
   <si>
+    <t>open-pit mining and beneficiation at Highland Valley</t>
+  </si>
+  <si>
     <t>market for copper, cathode</t>
   </si>
   <si>
+    <t>open-pit mining and beneficiation at Copper Mountain</t>
+  </si>
+  <si>
+    <t>underground mining and beneficiation at LaRonde</t>
+  </si>
+  <si>
+    <t>market for Cu concentrate</t>
+  </si>
+  <si>
+    <t>underground mining and beneficiation at New Afton</t>
+  </si>
+  <si>
+    <t>copper production, cathode, solvent extraction and electrowinning process</t>
+  </si>
+  <si>
+    <t>underground mining and beneficiation at Goldex</t>
+  </si>
+  <si>
+    <t>open-pit mining and beneficiation at Gibraltar</t>
+  </si>
+  <si>
+    <t>copper (Cu) global market</t>
+  </si>
+  <si>
+    <t>underground mining and beneficiation at Snow Lake</t>
+  </si>
+  <si>
+    <t>market for copper concentrate, sulfide ore</t>
+  </si>
+  <si>
+    <t>underground mining and beneficiation at Kidd Creek</t>
+  </si>
+  <si>
+    <t>open-pit mining and beneficiation at Mount Milligan</t>
+  </si>
+  <si>
     <t>copper mine operation and beneficiation, sulfide ore</t>
   </si>
   <si>
-    <t>market for copper concentrate, sulfide ore</t>
-  </si>
-  <si>
-    <t>copper production, cathode, solvent extraction and electrowinning process</t>
+    <t>open-pit mining and beneficiation at Mount Polley</t>
+  </si>
+  <si>
+    <t>CA-BC</t>
   </si>
   <si>
     <t>World</t>
   </si>
   <si>
+    <t>CA-QC</t>
+  </si>
+  <si>
     <t>CA</t>
   </si>
   <si>
-    <t>premise_generated_db_2025_L</t>
+    <t>GLO</t>
+  </si>
+  <si>
+    <t>CA-MB</t>
+  </si>
+  <si>
+    <t>CA-ON</t>
+  </si>
+  <si>
+    <t>premise_db_2025_L</t>
   </si>
 </sst>
 </file>
@@ -440,7 +533,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -483,25 +576,25 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F2" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="G2" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H2" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="I2">
-        <v>34.80889918131682</v>
+        <v>2.765184746397818</v>
       </c>
       <c r="J2">
-        <v>0.0002388457098937416</v>
+        <v>8.877422648596334E-05</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -515,25 +608,25 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="H3" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="I3">
-        <v>11.01301949429667</v>
+        <v>34.64763365897235</v>
       </c>
       <c r="J3">
-        <v>1.452414566649274E-05</v>
+        <v>0.000234690128195616</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -547,25 +640,25 @@
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F4" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="G4" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H4" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="I4">
-        <v>7.470196709385524</v>
+        <v>4.19575929041982</v>
       </c>
       <c r="J4">
-        <v>1.306314678559602E-05</v>
+        <v>0.0001518248648306356</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -579,25 +672,409 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H5" t="s">
+        <v>53</v>
+      </c>
+      <c r="I5">
+        <v>2.017888617591505</v>
+      </c>
+      <c r="J5">
+        <v>1.744619413725806E-05</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
         <v>13</v>
       </c>
-      <c r="E5" t="s">
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H6" t="s">
+        <v>53</v>
+      </c>
+      <c r="I6">
+        <v>143.5453336572545</v>
+      </c>
+      <c r="J6">
+        <v>0.001274879618740885</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
         <v>14</v>
       </c>
-      <c r="F5" t="s">
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" t="s">
+        <v>46</v>
+      </c>
+      <c r="H7" t="s">
+        <v>53</v>
+      </c>
+      <c r="I7">
+        <v>1.301956407110407</v>
+      </c>
+      <c r="J7">
+        <v>9.584738030272258E-06</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I8">
+        <v>51.8734823635929</v>
+      </c>
+      <c r="J8">
+        <v>5.765729680660986E-05</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" t="s">
+        <v>48</v>
+      </c>
+      <c r="H9" t="s">
+        <v>53</v>
+      </c>
+      <c r="I9">
+        <v>2.938122812506373</v>
+      </c>
+      <c r="J9">
+        <v>2.872203325238035E-05</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10" t="s">
+        <v>46</v>
+      </c>
+      <c r="H10" t="s">
+        <v>53</v>
+      </c>
+      <c r="I10">
+        <v>3.471408927701418</v>
+      </c>
+      <c r="J10">
+        <v>3.406426485666287E-05</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>28</v>
+      </c>
+      <c r="F11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G11" t="s">
+        <v>50</v>
+      </c>
+      <c r="H11" t="s">
+        <v>53</v>
+      </c>
+      <c r="I11">
+        <v>5.309223663121157</v>
+      </c>
+      <c r="J11">
+        <v>3.969843886266587E-05</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="1">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
         <v>19</v>
       </c>
-      <c r="G5" t="s">
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" t="s">
+        <v>40</v>
+      </c>
+      <c r="G12" t="s">
+        <v>51</v>
+      </c>
+      <c r="H12" t="s">
+        <v>53</v>
+      </c>
+      <c r="I12">
+        <v>1.777779313232829</v>
+      </c>
+      <c r="J12">
+        <v>2.294786226147066E-05</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="1">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13" t="s">
+        <v>41</v>
+      </c>
+      <c r="G13" t="s">
+        <v>47</v>
+      </c>
+      <c r="H13" t="s">
+        <v>53</v>
+      </c>
+      <c r="I13">
+        <v>7.384383745875441</v>
+      </c>
+      <c r="J13">
+        <v>1.196382882313784E-05</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="1">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
         <v>21</v>
       </c>
-      <c r="H5" t="s">
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" t="s">
+        <v>42</v>
+      </c>
+      <c r="G14" t="s">
+        <v>52</v>
+      </c>
+      <c r="H14" t="s">
+        <v>53</v>
+      </c>
+      <c r="I14">
+        <v>0.8509897704048344</v>
+      </c>
+      <c r="J14">
+        <v>7.94011517779509E-06</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="1">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
         <v>22</v>
       </c>
-      <c r="I5">
-        <v>50.77679741900687</v>
-      </c>
-      <c r="J5">
-        <v>5.172455386383114E-05</v>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" t="s">
+        <v>43</v>
+      </c>
+      <c r="G15" t="s">
+        <v>46</v>
+      </c>
+      <c r="H15" t="s">
+        <v>53</v>
+      </c>
+      <c r="I15">
+        <v>3.967816616137255</v>
+      </c>
+      <c r="J15">
+        <v>3.842351482291806E-05</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="1">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16" t="s">
+        <v>44</v>
+      </c>
+      <c r="G16" t="s">
+        <v>49</v>
+      </c>
+      <c r="H16" t="s">
+        <v>53</v>
+      </c>
+      <c r="I16">
+        <v>11.09926731708164</v>
+      </c>
+      <c r="J16">
+        <v>1.42166952939481E-05</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="1">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" t="s">
+        <v>26</v>
+      </c>
+      <c r="F17" t="s">
+        <v>45</v>
+      </c>
+      <c r="G17" t="s">
+        <v>46</v>
+      </c>
+      <c r="H17" t="s">
+        <v>53</v>
+      </c>
+      <c r="I17">
+        <v>6.353571754749084</v>
+      </c>
+      <c r="J17">
+        <v>6.915117629611321E-05</v>
       </c>
     </row>
   </sheetData>

--- a/results/LCA/lci_comparison_ab/copper_LCIA-results.xlsx
+++ b/results/LCA/lci_comparison_ab/copper_LCIA-results.xlsx
@@ -1,15 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/fasc_metal_sustainability/results/LCA/lci_comparison_ab/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_532D21E8F613C8264F2C4C73ED483ED55756F5B7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F380F33B-D301-497B-A91B-D23101925D15}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$1</definedName>
+  </definedNames>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -181,8 +190,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -199,12 +208,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -234,24 +255,37 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -289,7 +323,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -323,6 +357,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -357,9 +392,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -532,11 +568,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J17"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="119.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="68.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="85.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="78" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -565,44 +613,44 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="1">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>4</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="3">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="F2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G2" t="s">
-        <v>46</v>
-      </c>
-      <c r="H2" t="s">
-        <v>53</v>
-      </c>
-      <c r="I2">
-        <v>2.765184746397818</v>
-      </c>
-      <c r="J2">
-        <v>8.877422648596334E-05</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+      <c r="F2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I2" s="3">
+        <v>143.5453336572545</v>
+      </c>
+      <c r="J2" s="3">
+        <v>1.2748796187408849E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -613,28 +661,28 @@
       <c r="E3" t="s">
         <v>27</v>
       </c>
-      <c r="F3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I3">
-        <v>34.64763365897235</v>
-      </c>
-      <c r="J3">
-        <v>0.000234690128195616</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+      <c r="F3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I3" s="4">
+        <v>51.873482363592899</v>
+      </c>
+      <c r="J3" s="4">
+        <v>5.7657296806609862E-5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -643,30 +691,30 @@
         <v>25</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G4" t="s">
-        <v>46</v>
-      </c>
-      <c r="H4" t="s">
-        <v>53</v>
-      </c>
-      <c r="I4">
-        <v>4.19575929041982</v>
-      </c>
-      <c r="J4">
-        <v>0.0001518248648306356</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>29</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I4" s="4">
+        <v>11.09926731708164</v>
+      </c>
+      <c r="J4" s="4">
+        <v>1.42166952939481E-5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -678,27 +726,27 @@
         <v>26</v>
       </c>
       <c r="F5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H5" t="s">
         <v>53</v>
       </c>
       <c r="I5">
-        <v>2.017888617591505</v>
+        <v>2.7651847463978179</v>
       </c>
       <c r="J5">
-        <v>1.744619413725806E-05</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+        <v>8.877422648596334E-5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -710,22 +758,22 @@
         <v>26</v>
       </c>
       <c r="F6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H6" t="s">
         <v>53</v>
       </c>
       <c r="I6">
-        <v>143.5453336572545</v>
+        <v>4.1957592904198204</v>
       </c>
       <c r="J6">
-        <v>0.001274879618740885</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+        <v>1.518248648306356E-4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -751,18 +799,18 @@
         <v>53</v>
       </c>
       <c r="I7">
-        <v>1.301956407110407</v>
+        <v>1.3019564071104071</v>
       </c>
       <c r="J7">
-        <v>9.584738030272258E-06</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+        <v>9.5847380302722584E-6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -771,30 +819,30 @@
         <v>25</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H8" t="s">
         <v>53</v>
       </c>
       <c r="I8">
-        <v>51.8734823635929</v>
+        <v>3.4714089277014182</v>
       </c>
       <c r="J8">
-        <v>5.765729680660986E-05</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+        <v>3.4064264856662872E-5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -806,27 +854,27 @@
         <v>26</v>
       </c>
       <c r="F9" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H9" t="s">
         <v>53</v>
       </c>
       <c r="I9">
-        <v>2.938122812506373</v>
+        <v>3.967816616137255</v>
       </c>
       <c r="J9">
-        <v>2.872203325238035E-05</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
+        <v>3.8423514822918062E-5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -838,7 +886,7 @@
         <v>26</v>
       </c>
       <c r="F10" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="G10" t="s">
         <v>46</v>
@@ -847,18 +895,18 @@
         <v>53</v>
       </c>
       <c r="I10">
-        <v>3.471408927701418</v>
+        <v>6.3535717547490842</v>
       </c>
       <c r="J10">
-        <v>3.406426485666287E-05</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+        <v>6.9151176296113208E-5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -867,30 +915,30 @@
         <v>25</v>
       </c>
       <c r="E11" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H11" t="s">
         <v>53</v>
       </c>
       <c r="I11">
-        <v>5.309223663121157</v>
+        <v>1.777779313232829</v>
       </c>
       <c r="J11">
-        <v>3.969843886266587E-05</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+        <v>2.2947862261470658E-5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -902,27 +950,27 @@
         <v>26</v>
       </c>
       <c r="F12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H12" t="s">
         <v>53</v>
       </c>
       <c r="I12">
-        <v>1.777779313232829</v>
+        <v>0.85098977040483437</v>
       </c>
       <c r="J12">
-        <v>2.294786226147066E-05</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+        <v>7.9401151777950902E-6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -931,30 +979,30 @@
         <v>25</v>
       </c>
       <c r="E13" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F13" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="G13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H13" t="s">
         <v>53</v>
       </c>
       <c r="I13">
-        <v>7.384383745875441</v>
+        <v>2.0178886175915052</v>
       </c>
       <c r="J13">
-        <v>1.196382882313784E-05</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
+        <v>1.744619413725806E-5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -966,27 +1014,27 @@
         <v>26</v>
       </c>
       <c r="F14" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="G14" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H14" t="s">
         <v>53</v>
       </c>
       <c r="I14">
-        <v>0.8509897704048344</v>
+        <v>2.9381228125063732</v>
       </c>
       <c r="J14">
-        <v>7.94011517779509E-06</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
+        <v>2.8722033252380349E-5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -995,30 +1043,30 @@
         <v>25</v>
       </c>
       <c r="E15" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F15" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G15" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H15" t="s">
         <v>53</v>
       </c>
       <c r="I15">
-        <v>3.967816616137255</v>
+        <v>5.3092236631211573</v>
       </c>
       <c r="J15">
-        <v>3.842351482291806E-05</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
+        <v>3.9698438862665872E-5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -1027,57 +1075,62 @@
         <v>25</v>
       </c>
       <c r="E16" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I16" s="4">
+        <v>34.647633658972353</v>
+      </c>
+      <c r="J16" s="4">
+        <v>2.3469012819561601E-4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>11</v>
+      </c>
+      <c r="B17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" t="s">
         <v>29</v>
       </c>
-      <c r="F16" t="s">
-        <v>44</v>
-      </c>
-      <c r="G16" t="s">
-        <v>49</v>
-      </c>
-      <c r="H16" t="s">
-        <v>53</v>
-      </c>
-      <c r="I16">
-        <v>11.09926731708164</v>
-      </c>
-      <c r="J16">
-        <v>1.42166952939481E-05</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="1">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s">
-        <v>24</v>
-      </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-      <c r="D17" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" t="s">
-        <v>26</v>
-      </c>
-      <c r="F17" t="s">
-        <v>45</v>
-      </c>
-      <c r="G17" t="s">
-        <v>46</v>
-      </c>
-      <c r="H17" t="s">
-        <v>53</v>
-      </c>
-      <c r="I17">
-        <v>6.353571754749084</v>
-      </c>
-      <c r="J17">
-        <v>6.915117629611321E-05</v>
+      <c r="F17" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I17" s="4">
+        <v>7.3843837458754411</v>
+      </c>
+      <c r="J17" s="4">
+        <v>1.196382882313784E-5</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:J1" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J17">
+      <sortCondition ref="G1"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>